--- a/data/models/firefly.xlsx
+++ b/data/models/firefly.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t xml:space="preserve">LDB FINANCE</t>
   </si>
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Firefly Aerospace (FLY)</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario model: 2030 earning power, capitalised and discounted back four years  ·  Inputs in blue can be changed; everything else recalculates.</t>
+    <t xml:space="preserve">Scenario model: 2030 earning power, capitalised and discounted back four years, plus cash flow along the way  ·  Inputs in blue can be changed; everything else recalculates.</t>
   </si>
   <si>
     <t xml:space="preserve">SCENARIOS</t>
@@ -110,6 +110,18 @@
     <t xml:space="preserve">Shares by 2030 (billions)</t>
   </si>
   <si>
+    <t xml:space="preserve">Free cash flow this year ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating cash flow less capital spending, last twelve months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free cash flow in 2030, share of after-tax profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rest is reinvested; zero for a company without profit yet</t>
+  </si>
+  <si>
     <t xml:space="preserve">VALUE</t>
   </si>
   <si>
@@ -119,7 +131,25 @@
     <t xml:space="preserve">Value today ($B)</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus net cash: equity value ($B)</t>
+    <t xml:space="preserve">Free cash flow in 2030 ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free cash flow, year 1 ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free cash flow, year 2 ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free cash flow, year 3 ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free cash flow, year 4 ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Present value of free cash flow, years 1-4 ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus cash flow and net cash: equity value ($B)</t>
   </si>
 </sst>
 </file>
@@ -743,16 +773,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="n">
-        <f aca="false">Model!B20</f>
-        <v>4.00227271915123</v>
+        <f aca="false">Model!B28</f>
+        <v>2.62845419363138</v>
       </c>
       <c r="C8" s="10" t="n">
-        <f aca="false">Model!C20</f>
-        <v>19.6244295868011</v>
+        <f aca="false">Model!C28</f>
+        <v>18.1392203700229</v>
       </c>
       <c r="D8" s="10" t="n">
-        <f aca="false">Model!D20</f>
-        <v>51.9336218304919</v>
+        <f aca="false">Model!D28</f>
+        <v>50.4071568021365</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -775,7 +805,7 @@
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">SUMPRODUCT(B8:D8,B9:D9)</f>
-        <v>23.7961884308113</v>
+        <v>22.3285129339534</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -792,7 +822,7 @@
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">C10/C11-1</f>
-        <v>0.366811512395825</v>
+        <v>0.282510794598127</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -821,8 +851,8 @@
         <v>0.13</v>
       </c>
       <c r="C16" s="18" t="n">
-        <f aca="false">(Model!$C$17/(1+B16)^Model!$C$11+Model!$C$12)/Model!$C$13</f>
-        <v>20.9724992760879</v>
+        <f aca="false">(Model!$C$19/(1+B16)^Model!$C$11+Model!$C$22/(1+B16)^1+Model!$C$23/(1+B16)^2+Model!$C$24/(1+B16)^3+Model!$C$25/(1+B16)^4+Model!$C$12)/Model!$C$13</f>
+        <v>19.4451094373009</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -831,8 +861,8 @@
         <v>0.14</v>
       </c>
       <c r="C17" s="18" t="n">
-        <f aca="false">(Model!$C$17/(1+B17)^Model!$C$11+Model!$C$12)/Model!$C$13</f>
-        <v>20.2836846714656</v>
+        <f aca="false">(Model!$C$19/(1+B17)^Model!$C$11+Model!$C$22/(1+B17)^1+Model!$C$23/(1+B17)^2+Model!$C$24/(1+B17)^3+Model!$C$25/(1+B17)^4+Model!$C$12)/Model!$C$13</f>
+        <v>18.7776553880635</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -841,8 +871,8 @@
         <v>0.15</v>
       </c>
       <c r="C18" s="18" t="n">
-        <f aca="false">(Model!$C$17/(1+B18)^Model!$C$11+Model!$C$12)/Model!$C$13</f>
-        <v>19.6244295868011</v>
+        <f aca="false">(Model!$C$19/(1+B18)^Model!$C$11+Model!$C$22/(1+B18)^1+Model!$C$23/(1+B18)^2+Model!$C$24/(1+B18)^3+Model!$C$25/(1+B18)^4+Model!$C$12)/Model!$C$13</f>
+        <v>18.1392203700229</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -851,8 +881,8 @@
         <v>0.16</v>
       </c>
       <c r="C19" s="18" t="n">
-        <f aca="false">(Model!$C$17/(1+B19)^Model!$C$11+Model!$C$12)/Model!$C$13</f>
-        <v>18.9932247961235</v>
+        <f aca="false">(Model!$C$19/(1+B19)^Model!$C$11+Model!$C$22/(1+B19)^1+Model!$C$23/(1+B19)^2+Model!$C$24/(1+B19)^3+Model!$C$25/(1+B19)^4+Model!$C$12)/Model!$C$13</f>
+        <v>17.5283142748761</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -861,8 +891,8 @@
         <v>0.17</v>
       </c>
       <c r="C20" s="18" t="n">
-        <f aca="false">(Model!$C$17/(1+B20)^Model!$C$11+Model!$C$12)/Model!$C$13</f>
-        <v>18.3886502129673</v>
+        <f aca="false">(Model!$C$19/(1+B20)^Model!$C$11+Model!$C$22/(1+B20)^1+Model!$C$23/(1+B20)^2+Model!$C$24/(1+B20)^3+Model!$C$25/(1+B20)^4+Model!$C$12)/Model!$C$13</f>
+        <v>16.9435352789197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -910,7 +940,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -1060,93 +1090,229 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8" t="s">
+      <c r="B14" s="20" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="24" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="24" t="n">
         <f aca="false">B8*B9</f>
         <v>1.4</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C19" s="24" t="n">
         <f aca="false">C8*C9</f>
         <v>6</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D19" s="24" t="n">
         <f aca="false">D8*D9</f>
         <v>16</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="24" t="n">
-        <f aca="false">B17/(1+B10)^B11</f>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <f aca="false">B19/(1+B10)^B11</f>
         <v>0.800454543830247</v>
       </c>
-      <c r="C18" s="24" t="n">
-        <f aca="false">C17/(1+C10)^C11</f>
+      <c r="C20" s="24" t="n">
+        <f aca="false">C19/(1+C10)^C11</f>
         <v>3.4305194735582</v>
       </c>
-      <c r="D18" s="24" t="n">
-        <f aca="false">D17/(1+D10)^D11</f>
+      <c r="D20" s="24" t="n">
+        <f aca="false">D19/(1+D10)^D11</f>
         <v>9.14805192948854</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="24" t="n">
-        <f aca="false">B18+B12</f>
-        <v>0.800454543830247</v>
-      </c>
-      <c r="C19" s="24" t="n">
-        <f aca="false">C18+C12</f>
-        <v>3.6305194735582</v>
-      </c>
-      <c r="D19" s="24" t="n">
-        <f aca="false">D18+D12</f>
-        <v>9.34805192948853</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <f aca="false">B14+(B21-B14)*1/B11</f>
+        <v>-0.1725</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <f aca="false">C14+(C21-C14)*1/C11</f>
+        <v>-0.1725</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <f aca="false">D14+(D21-D14)*1/D11</f>
+        <v>-0.1725</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <f aca="false">B14+(B21-B14)*2/B11</f>
+        <v>-0.115</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <f aca="false">C14+(C21-C14)*2/C11</f>
+        <v>-0.115</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <f aca="false">D14+(D21-D14)*2/D11</f>
+        <v>-0.115</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <f aca="false">B14+(B21-B14)*3/B11</f>
+        <v>-0.0575</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <f aca="false">C14+(C21-C14)*3/C11</f>
+        <v>-0.0575</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <f aca="false">D14+(D21-D14)*3/D11</f>
+        <v>-0.0575</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <f aca="false">B14+(B21-B14)*4/B11</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <f aca="false">C14+(C21-C14)*4/C11</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <f aca="false">D14+(D21-D14)*4/D11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <f aca="false">B22/(1+B10)^1+B23/(1+B10)^2+B24/(1+B10)^3+B25/(1+B10)^4</f>
+        <v>-0.27476370510397</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <f aca="false">C22/(1+C10)^1+C23/(1+C10)^2+C24/(1+C10)^3+C25/(1+C10)^4</f>
+        <v>-0.27476370510397</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <f aca="false">D22/(1+D10)^1+D23/(1+D10)^2+D24/(1+D10)^3+D25/(1+D10)^4</f>
+        <v>-0.27476370510397</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <f aca="false">B20+B26+B12</f>
+        <v>0.525690838726277</v>
+      </c>
+      <c r="C27" s="24" t="n">
+        <f aca="false">C20+C26+C12</f>
+        <v>3.35575576845423</v>
+      </c>
+      <c r="D27" s="24" t="n">
+        <f aca="false">D20+D26+D12</f>
+        <v>9.07328822438456</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="13" t="n">
-        <f aca="false">B19/B13</f>
-        <v>4.00227271915123</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <f aca="false">C19/C13</f>
-        <v>19.6244295868011</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <f aca="false">D19/D13</f>
-        <v>51.9336218304919</v>
+      <c r="B28" s="13" t="n">
+        <f aca="false">B27/B13</f>
+        <v>2.62845419363138</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <f aca="false">C27/C13</f>
+        <v>18.1392203700229</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <f aca="false">D27/D13</f>
+        <v>50.4071568021365</v>
       </c>
     </row>
   </sheetData>
